--- a/backend/watch/PRECOS AMAKHA PARIS JULHO.xlsx
+++ b/backend/watch/PRECOS AMAKHA PARIS JULHO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.0.0.20\Compras\1.COMPRAS\PRECOS SUBIDOS SIRIUS\FALTA SUBIR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A1D10CD-8031-4852-A1DA-697EDD5F073F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1436B6ED-D786-44F7-BBCB-BED6B18F721E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32715" yWindow="3090" windowWidth="16200" windowHeight="11565" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-35280" yWindow="3180" windowWidth="16200" windowHeight="11565" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -415,7 +415,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:L317"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -459,10 +459,10 @@
         <v>7898662436427</v>
       </c>
       <c r="F2" s="5">
-        <v>14.6</v>
+        <v>14.25</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>909</v>
@@ -476,10 +476,10 @@
         <v>7898662436144</v>
       </c>
       <c r="F3" s="5">
-        <v>14.6</v>
+        <v>14.25</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>909</v>
@@ -493,10 +493,10 @@
         <v>7898662436274</v>
       </c>
       <c r="F4" s="5">
-        <v>14.6</v>
+        <v>14.25</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <v>909</v>
@@ -507,13 +507,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>7898662430531</v>
+        <v>7898662431057</v>
       </c>
       <c r="F5" s="5">
-        <v>14.6</v>
+        <v>14.25</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>909</v>
@@ -524,13 +524,13 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>7898662430920</v>
+        <v>7898662430791</v>
       </c>
       <c r="F6" s="5">
-        <v>14.6</v>
+        <v>14.25</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>909</v>
@@ -541,13 +541,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>7898662430470</v>
+        <v>7898662431064</v>
       </c>
       <c r="F7" s="5">
-        <v>14.6</v>
+        <v>14.25</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <v>909</v>
@@ -558,13 +558,13 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>7898662436434</v>
+        <v>7898662431002</v>
       </c>
       <c r="F8" s="5">
-        <v>14.6</v>
+        <v>14.25</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H8">
         <v>909</v>
@@ -575,13 +575,13 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>7898662436137</v>
+        <v>7898662430975</v>
       </c>
       <c r="F9" s="5">
-        <v>14.6</v>
+        <v>14.25</v>
       </c>
       <c r="G9">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H9">
         <v>909</v>
@@ -592,13 +592,13 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>7898662436847</v>
+        <v>7898662430722</v>
       </c>
       <c r="F10" s="5">
-        <v>29.9</v>
+        <v>14.25</v>
       </c>
       <c r="G10">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H10">
         <v>909</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>7898662436274</v>
+        <v>7898662430487</v>
       </c>
       <c r="F11" s="5">
         <v>14.25</v>
@@ -643,7 +643,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>7898662430531</v>
+        <v>7898662430524</v>
       </c>
       <c r="F13" s="5">
         <v>14.25</v>
@@ -660,7 +660,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>7898662430920</v>
+        <v>7898662430531</v>
       </c>
       <c r="F14" s="5">
         <v>14.25</v>
@@ -677,7 +677,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>7898662430517</v>
+        <v>7898662430920</v>
       </c>
       <c r="F15" s="5">
         <v>14.25</v>
@@ -694,7 +694,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>7898662436434</v>
+        <v>7898662430883</v>
       </c>
       <c r="F16" s="5">
         <v>14.25</v>
@@ -711,7 +711,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>7898662436137</v>
+        <v>7898662430470</v>
       </c>
       <c r="F17" s="5">
         <v>14.25</v>
@@ -728,7 +728,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>7898662430852</v>
+        <v>7898662430517</v>
       </c>
       <c r="F18" s="5">
         <v>14.25</v>
@@ -745,13 +745,13 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>7898662436427</v>
+        <v>7898662430401</v>
       </c>
       <c r="F19" s="5">
-        <v>14.6</v>
+        <v>14.25</v>
       </c>
       <c r="G19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H19">
         <v>909</v>
@@ -762,13 +762,13 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>7898662436144</v>
+        <v>7898662430807</v>
       </c>
       <c r="F20" s="5">
-        <v>14.6</v>
+        <v>14.25</v>
       </c>
       <c r="G20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H20">
         <v>909</v>
@@ -779,13 +779,13 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>7898662436274</v>
+        <v>7898662434430</v>
       </c>
       <c r="F21" s="5">
-        <v>14.6</v>
+        <v>14.25</v>
       </c>
       <c r="G21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H21">
         <v>909</v>
@@ -796,13 +796,13 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>7898662430487</v>
+        <v>7898662435093</v>
       </c>
       <c r="F22" s="5">
-        <v>14.6</v>
+        <v>14.25</v>
       </c>
       <c r="G22">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H22">
         <v>909</v>
@@ -813,13 +813,13 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>7898662430845</v>
+        <v>7898662430425</v>
       </c>
       <c r="F23" s="5">
-        <v>14.6</v>
+        <v>14.25</v>
       </c>
       <c r="G23">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H23">
         <v>909</v>
@@ -830,13 +830,13 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>7898662430531</v>
+        <v>7898662436434</v>
       </c>
       <c r="F24" s="5">
-        <v>14.6</v>
+        <v>14.25</v>
       </c>
       <c r="G24">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H24">
         <v>909</v>
@@ -847,13 +847,13 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>7898662430920</v>
+        <v>7898662436137</v>
       </c>
       <c r="F25" s="5">
-        <v>14.6</v>
+        <v>14.25</v>
       </c>
       <c r="G25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H25">
         <v>909</v>
@@ -864,13 +864,13 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>7898662430470</v>
+        <v>7898662436267</v>
       </c>
       <c r="F26" s="5">
-        <v>14.6</v>
+        <v>14.25</v>
       </c>
       <c r="G26">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H26">
         <v>909</v>
@@ -881,13 +881,13 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>7898662436434</v>
+        <v>7898662430951</v>
       </c>
       <c r="F27" s="5">
-        <v>14.6</v>
+        <v>14.25</v>
       </c>
       <c r="G27">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H27">
         <v>909</v>
@@ -898,13 +898,13 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>7898662436137</v>
+        <v>7898662430869</v>
       </c>
       <c r="F28" s="5">
-        <v>14.6</v>
+        <v>14.25</v>
       </c>
       <c r="G28">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H28">
         <v>909</v>
@@ -915,13 +915,13 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>7898662430951</v>
+        <v>7898662430913</v>
       </c>
       <c r="F29" s="5">
-        <v>14.6</v>
+        <v>14.25</v>
       </c>
       <c r="G29">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H29">
         <v>909</v>
@@ -935,10 +935,10 @@
         <v>7898662430852</v>
       </c>
       <c r="F30" s="5">
-        <v>14.6</v>
+        <v>14.25</v>
       </c>
       <c r="G30">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H30">
         <v>909</v>
@@ -949,13 +949,13 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>7898662434423</v>
+        <v>7898662430463</v>
       </c>
       <c r="F31" s="5">
-        <v>14.6</v>
+        <v>14.25</v>
       </c>
       <c r="G31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H31">
         <v>909</v>
@@ -966,13 +966,13 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>7898662436762</v>
+        <v>7898662430746</v>
       </c>
       <c r="F32" s="5">
-        <v>17.95</v>
+        <v>14.25</v>
       </c>
       <c r="G32">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H32">
         <v>909</v>
@@ -983,13 +983,13 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>7898662436724</v>
+        <v>7898662430418</v>
       </c>
       <c r="F33" s="5">
-        <v>29.9</v>
+        <v>14.25</v>
       </c>
       <c r="G33">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H33">
         <v>909</v>
@@ -1000,13 +1000,13 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>7898662436793</v>
+        <v>7898662430500</v>
       </c>
       <c r="F34" s="5">
-        <v>29.9</v>
+        <v>14.25</v>
       </c>
       <c r="G34">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H34">
         <v>909</v>
@@ -1017,13 +1017,13 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>7898662436847</v>
+        <v>7898662434201</v>
       </c>
       <c r="F35" s="5">
-        <v>29.9</v>
+        <v>14.25</v>
       </c>
       <c r="G35">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H35">
         <v>909</v>
@@ -1034,13 +1034,13 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>7898662431057</v>
+        <v>7898662434423</v>
       </c>
       <c r="F36" s="5">
-        <v>14.6</v>
+        <v>14.25</v>
       </c>
       <c r="G36">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H36">
         <v>909</v>
@@ -1051,13 +1051,13 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>7898662430746</v>
+        <v>7898662434966</v>
       </c>
       <c r="F37" s="5">
-        <v>14.6</v>
+        <v>14.25</v>
       </c>
       <c r="G37">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H37">
         <v>909</v>
@@ -1068,13 +1068,13 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>7898662432672</v>
+        <v>7898662430555</v>
       </c>
       <c r="F38" s="5">
-        <v>58.1</v>
+        <v>14.25</v>
       </c>
       <c r="G38">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H38">
         <v>909</v>
@@ -1085,13 +1085,13 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>7898662433877</v>
+        <v>7898662435147</v>
       </c>
       <c r="F39" s="5">
-        <v>11.66</v>
+        <v>14.25</v>
       </c>
       <c r="G39">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H39">
         <v>909</v>
@@ -1102,13 +1102,13 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>7898662436427</v>
+        <v>7898662435208</v>
       </c>
       <c r="F40" s="5">
-        <v>13.85</v>
+        <v>14.25</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H40">
         <v>909</v>
@@ -1119,13 +1119,13 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>7898662436144</v>
+        <v>7898662435123</v>
       </c>
       <c r="F41" s="5">
-        <v>13.85</v>
+        <v>14.25</v>
       </c>
       <c r="G41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H41">
         <v>909</v>
@@ -1136,13 +1136,13 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>7898662436274</v>
+        <v>7898662435031</v>
       </c>
       <c r="F42" s="5">
-        <v>13.85</v>
+        <v>14.25</v>
       </c>
       <c r="G42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H42">
         <v>909</v>
@@ -1153,13 +1153,13 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>7898662430487</v>
+        <v>7898662436410</v>
       </c>
       <c r="F43" s="5">
-        <v>13.85</v>
+        <v>56.6</v>
       </c>
       <c r="G43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H43">
         <v>909</v>
@@ -1170,13 +1170,13 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>7898662430531</v>
+        <v>7898662434249</v>
       </c>
       <c r="F44" s="5">
-        <v>13.85</v>
+        <v>56.6</v>
       </c>
       <c r="G44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H44">
         <v>909</v>
@@ -1187,13 +1187,13 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>7898662430920</v>
+        <v>7898662432726</v>
       </c>
       <c r="F45" s="5">
-        <v>13.85</v>
+        <v>56.6</v>
       </c>
       <c r="G45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H45">
         <v>909</v>
@@ -1204,13 +1204,13 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>7898662430470</v>
+        <v>7898662432733</v>
       </c>
       <c r="F46" s="5">
-        <v>13.85</v>
+        <v>56.6</v>
       </c>
       <c r="G46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H46">
         <v>909</v>
@@ -1221,13 +1221,13 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>7898662435093</v>
+        <v>7898662432665</v>
       </c>
       <c r="F47" s="5">
-        <v>13.85</v>
+        <v>56.6</v>
       </c>
       <c r="G47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H47">
         <v>909</v>
@@ -1238,13 +1238,13 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>7898662436434</v>
+        <v>7898662432740</v>
       </c>
       <c r="F48" s="5">
-        <v>13.85</v>
+        <v>56.6</v>
       </c>
       <c r="G48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H48">
         <v>909</v>
@@ -1255,13 +1255,13 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>7898662436137</v>
+        <v>7898662434539</v>
       </c>
       <c r="F49" s="5">
-        <v>13.85</v>
+        <v>56.6</v>
       </c>
       <c r="G49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H49">
         <v>909</v>
@@ -1272,13 +1272,13 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>7898662436267</v>
+        <v>7898662435109</v>
       </c>
       <c r="F50" s="5">
-        <v>13.85</v>
+        <v>56.6</v>
       </c>
       <c r="G50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H50">
         <v>909</v>
@@ -1289,13 +1289,13 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>7898662430852</v>
+        <v>7898662436403</v>
       </c>
       <c r="F51" s="5">
-        <v>13.85</v>
+        <v>56.6</v>
       </c>
       <c r="G51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H51">
         <v>909</v>
@@ -1306,13 +1306,13 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>7898662435147</v>
+        <v>7898662434546</v>
       </c>
       <c r="F52" s="5">
-        <v>13.85</v>
+        <v>56.6</v>
       </c>
       <c r="G52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H52">
         <v>909</v>
@@ -1323,13 +1323,13 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>7898662436793</v>
+        <v>7898662432672</v>
       </c>
       <c r="F53" s="5">
-        <v>27.4</v>
+        <v>56.6</v>
       </c>
       <c r="G53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H53">
         <v>909</v>
@@ -1340,13 +1340,13 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>7898662436847</v>
+        <v>7898662432719</v>
       </c>
       <c r="F54" s="5">
-        <v>27.4</v>
+        <v>56.6</v>
       </c>
       <c r="G54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H54">
         <v>909</v>
@@ -1357,13 +1357,13 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>7898662431057</v>
+        <v>7898662434232</v>
       </c>
       <c r="F55" s="5">
-        <v>13.85</v>
+        <v>56.6</v>
       </c>
       <c r="G55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H55">
         <v>909</v>
@@ -1374,13 +1374,13 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>7898662430746</v>
+        <v>7898662432658</v>
       </c>
       <c r="F56" s="5">
-        <v>13.85</v>
+        <v>56.6</v>
       </c>
       <c r="G56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H56">
         <v>909</v>
@@ -1391,18 +1391,4438 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
+        <v>7898662435116</v>
+      </c>
+      <c r="F57" s="5">
+        <v>56.6</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+      <c r="H57">
+        <v>909</v>
+      </c>
+      <c r="L57" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>7898662433877</v>
+      </c>
+      <c r="F58" s="5">
+        <v>9.74</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+      <c r="H58">
+        <v>909</v>
+      </c>
+      <c r="L58" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>7898662433839</v>
+      </c>
+      <c r="F59" s="5">
+        <v>9.74</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+      <c r="H59">
+        <v>909</v>
+      </c>
+      <c r="L59" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>7898662435130</v>
+      </c>
+      <c r="F60" s="5">
+        <v>9.74</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+      <c r="H60">
+        <v>909</v>
+      </c>
+      <c r="L60" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>7898662433860</v>
+      </c>
+      <c r="F61" s="5">
+        <v>9.74</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="H61">
+        <v>909</v>
+      </c>
+      <c r="L61" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>7898662433853</v>
+      </c>
+      <c r="F62" s="5">
+        <v>9.74</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
+      <c r="H62">
+        <v>909</v>
+      </c>
+      <c r="L62" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>7898662433822</v>
+      </c>
+      <c r="F63" s="5">
+        <v>9.74</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="H63">
+        <v>909</v>
+      </c>
+      <c r="L63" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>7898662436298</v>
+      </c>
+      <c r="F64" s="5">
+        <v>18.079999999999998</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64">
+        <v>909</v>
+      </c>
+      <c r="L64" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>7898662436304</v>
+      </c>
+      <c r="F65" s="5">
+        <v>18.079999999999998</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65">
+        <v>909</v>
+      </c>
+      <c r="L65" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>7898662436182</v>
+      </c>
+      <c r="F66" s="5">
+        <v>18.079999999999998</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66">
+        <v>909</v>
+      </c>
+      <c r="L66" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>7898662436175</v>
+      </c>
+      <c r="F67" s="5">
+        <v>18.079999999999998</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67">
+        <v>909</v>
+      </c>
+      <c r="L67" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>7898662436199</v>
+      </c>
+      <c r="F68" s="5">
+        <v>18.079999999999998</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+      <c r="H68">
+        <v>909</v>
+      </c>
+      <c r="L68" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>7898662436762</v>
+      </c>
+      <c r="F69" s="5">
+        <v>18.079999999999998</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+      <c r="H69">
+        <v>909</v>
+      </c>
+      <c r="L69" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>7898662436816</v>
+      </c>
+      <c r="F70" s="5">
+        <v>18.079999999999998</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+      <c r="H70">
+        <v>909</v>
+      </c>
+      <c r="L70" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>7898662436380</v>
+      </c>
+      <c r="F71" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G71">
+        <v>1</v>
+      </c>
+      <c r="H71">
+        <v>909</v>
+      </c>
+      <c r="L71" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>7898662436397</v>
+      </c>
+      <c r="F72" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+      <c r="H72">
+        <v>909</v>
+      </c>
+      <c r="L72" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>7898662436373</v>
+      </c>
+      <c r="F73" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
+      <c r="H73">
+        <v>909</v>
+      </c>
+      <c r="L73" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>7898662436724</v>
+      </c>
+      <c r="F74" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G74">
+        <v>1</v>
+      </c>
+      <c r="H74">
+        <v>909</v>
+      </c>
+      <c r="L74" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>7898662436731</v>
+      </c>
+      <c r="F75" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+      <c r="H75">
+        <v>909</v>
+      </c>
+      <c r="L75" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>7898662436793</v>
+      </c>
+      <c r="F76" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+      <c r="H76">
+        <v>909</v>
+      </c>
+      <c r="L76" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>7898662436847</v>
+      </c>
+      <c r="F77" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+      <c r="H77">
+        <v>909</v>
+      </c>
+      <c r="L77" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>7898662436106</v>
+      </c>
+      <c r="F78" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+      <c r="H78">
+        <v>909</v>
+      </c>
+      <c r="L78" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>7898662435550</v>
+      </c>
+      <c r="F79" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G79">
+        <v>1</v>
+      </c>
+      <c r="H79">
+        <v>909</v>
+      </c>
+      <c r="L79" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>7898662436090</v>
+      </c>
+      <c r="F80" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G80">
+        <v>1</v>
+      </c>
+      <c r="H80">
+        <v>909</v>
+      </c>
+      <c r="L80" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>7898662436427</v>
+      </c>
+      <c r="F81" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G81">
+        <v>3</v>
+      </c>
+      <c r="H81">
+        <v>909</v>
+      </c>
+      <c r="L81" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>7898662436144</v>
+      </c>
+      <c r="F82" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G82">
+        <v>3</v>
+      </c>
+      <c r="H82">
+        <v>909</v>
+      </c>
+      <c r="L82" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>7898662436274</v>
+      </c>
+      <c r="F83" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G83">
+        <v>3</v>
+      </c>
+      <c r="H83">
+        <v>909</v>
+      </c>
+      <c r="L83" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>7898662431057</v>
+      </c>
+      <c r="F84" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G84">
+        <v>3</v>
+      </c>
+      <c r="H84">
+        <v>909</v>
+      </c>
+      <c r="L84" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>7898662430791</v>
+      </c>
+      <c r="F85" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G85">
+        <v>3</v>
+      </c>
+      <c r="H85">
+        <v>909</v>
+      </c>
+      <c r="L85" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>7898662431064</v>
+      </c>
+      <c r="F86" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G86">
+        <v>3</v>
+      </c>
+      <c r="H86">
+        <v>909</v>
+      </c>
+      <c r="L86" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>7898662431002</v>
+      </c>
+      <c r="F87" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G87">
+        <v>3</v>
+      </c>
+      <c r="H87">
+        <v>909</v>
+      </c>
+      <c r="L87" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>7898662430975</v>
+      </c>
+      <c r="F88" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G88">
+        <v>3</v>
+      </c>
+      <c r="H88">
+        <v>909</v>
+      </c>
+      <c r="L88" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>7898662430722</v>
+      </c>
+      <c r="F89" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G89">
+        <v>3</v>
+      </c>
+      <c r="H89">
+        <v>909</v>
+      </c>
+      <c r="L89" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>7898662430487</v>
+      </c>
+      <c r="F90" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G90">
+        <v>3</v>
+      </c>
+      <c r="H90">
+        <v>909</v>
+      </c>
+      <c r="L90" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>7898662430845</v>
+      </c>
+      <c r="F91" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G91">
+        <v>3</v>
+      </c>
+      <c r="H91">
+        <v>909</v>
+      </c>
+      <c r="L91" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>7898662430524</v>
+      </c>
+      <c r="F92" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G92">
+        <v>3</v>
+      </c>
+      <c r="H92">
+        <v>909</v>
+      </c>
+      <c r="L92" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>7898662430531</v>
+      </c>
+      <c r="F93" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G93">
+        <v>3</v>
+      </c>
+      <c r="H93">
+        <v>909</v>
+      </c>
+      <c r="L93" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>7898662430920</v>
+      </c>
+      <c r="F94" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G94">
+        <v>3</v>
+      </c>
+      <c r="H94">
+        <v>909</v>
+      </c>
+      <c r="L94" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>7898662430883</v>
+      </c>
+      <c r="F95" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G95">
+        <v>3</v>
+      </c>
+      <c r="H95">
+        <v>909</v>
+      </c>
+      <c r="L95" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <v>7898662430470</v>
+      </c>
+      <c r="F96" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G96">
+        <v>3</v>
+      </c>
+      <c r="H96">
+        <v>909</v>
+      </c>
+      <c r="L96" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
+        <v>7898662430517</v>
+      </c>
+      <c r="F97" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G97">
+        <v>3</v>
+      </c>
+      <c r="H97">
+        <v>909</v>
+      </c>
+      <c r="L97" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
+        <v>7898662430401</v>
+      </c>
+      <c r="F98" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G98">
+        <v>3</v>
+      </c>
+      <c r="H98">
+        <v>909</v>
+      </c>
+      <c r="L98" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>7898662430807</v>
+      </c>
+      <c r="F99" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G99">
+        <v>3</v>
+      </c>
+      <c r="H99">
+        <v>909</v>
+      </c>
+      <c r="L99" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>7898662434430</v>
+      </c>
+      <c r="F100" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G100">
+        <v>3</v>
+      </c>
+      <c r="H100">
+        <v>909</v>
+      </c>
+      <c r="L100" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
+        <v>7898662435093</v>
+      </c>
+      <c r="F101" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G101">
+        <v>3</v>
+      </c>
+      <c r="H101">
+        <v>909</v>
+      </c>
+      <c r="L101" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
+        <v>7898662430425</v>
+      </c>
+      <c r="F102" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G102">
+        <v>3</v>
+      </c>
+      <c r="H102">
+        <v>909</v>
+      </c>
+      <c r="L102" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
+        <v>7898662436434</v>
+      </c>
+      <c r="F103" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G103">
+        <v>3</v>
+      </c>
+      <c r="H103">
+        <v>909</v>
+      </c>
+      <c r="L103" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
+        <v>7898662436137</v>
+      </c>
+      <c r="F104" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G104">
+        <v>3</v>
+      </c>
+      <c r="H104">
+        <v>909</v>
+      </c>
+      <c r="L104" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
+        <v>7898662436267</v>
+      </c>
+      <c r="F105" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G105">
+        <v>3</v>
+      </c>
+      <c r="H105">
+        <v>909</v>
+      </c>
+      <c r="L105" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
+        <v>7898662430951</v>
+      </c>
+      <c r="F106" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G106">
+        <v>3</v>
+      </c>
+      <c r="H106">
+        <v>909</v>
+      </c>
+      <c r="L106" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
+        <v>7898662430869</v>
+      </c>
+      <c r="F107" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G107">
+        <v>3</v>
+      </c>
+      <c r="H107">
+        <v>909</v>
+      </c>
+      <c r="L107" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
+        <v>7898662430913</v>
+      </c>
+      <c r="F108" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G108">
+        <v>3</v>
+      </c>
+      <c r="H108">
+        <v>909</v>
+      </c>
+      <c r="L108" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
+        <v>7898662430852</v>
+      </c>
+      <c r="F109" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G109">
+        <v>3</v>
+      </c>
+      <c r="H109">
+        <v>909</v>
+      </c>
+      <c r="L109" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
+        <v>7898662430463</v>
+      </c>
+      <c r="F110" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G110">
+        <v>3</v>
+      </c>
+      <c r="H110">
+        <v>909</v>
+      </c>
+      <c r="L110" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
+        <v>7898662430746</v>
+      </c>
+      <c r="F111" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G111">
+        <v>3</v>
+      </c>
+      <c r="H111">
+        <v>909</v>
+      </c>
+      <c r="L111" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
+        <v>7898662430418</v>
+      </c>
+      <c r="F112" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G112">
+        <v>3</v>
+      </c>
+      <c r="H112">
+        <v>909</v>
+      </c>
+      <c r="L112" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
+        <v>7898662430500</v>
+      </c>
+      <c r="F113" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G113">
+        <v>3</v>
+      </c>
+      <c r="H113">
+        <v>909</v>
+      </c>
+      <c r="L113" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
+        <v>7898662434201</v>
+      </c>
+      <c r="F114" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G114">
+        <v>3</v>
+      </c>
+      <c r="H114">
+        <v>909</v>
+      </c>
+      <c r="L114" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
+        <v>7898662434423</v>
+      </c>
+      <c r="F115" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G115">
+        <v>3</v>
+      </c>
+      <c r="H115">
+        <v>909</v>
+      </c>
+      <c r="L115" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
+        <v>7898662434966</v>
+      </c>
+      <c r="F116" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G116">
+        <v>3</v>
+      </c>
+      <c r="H116">
+        <v>909</v>
+      </c>
+      <c r="L116" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
+        <v>7898662430555</v>
+      </c>
+      <c r="F117" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G117">
+        <v>3</v>
+      </c>
+      <c r="H117">
+        <v>909</v>
+      </c>
+      <c r="L117" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
+        <v>7898662435147</v>
+      </c>
+      <c r="F118" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G118">
+        <v>3</v>
+      </c>
+      <c r="H118">
+        <v>909</v>
+      </c>
+      <c r="L118" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
+        <v>7898662435208</v>
+      </c>
+      <c r="F119" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G119">
+        <v>3</v>
+      </c>
+      <c r="H119">
+        <v>909</v>
+      </c>
+      <c r="L119" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
+        <v>7898662435123</v>
+      </c>
+      <c r="F120" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G120">
+        <v>3</v>
+      </c>
+      <c r="H120">
+        <v>909</v>
+      </c>
+      <c r="L120" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
+        <v>7898662435031</v>
+      </c>
+      <c r="F121" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="G121">
+        <v>3</v>
+      </c>
+      <c r="H121">
+        <v>909</v>
+      </c>
+      <c r="L121" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
+        <v>7898662436410</v>
+      </c>
+      <c r="F122" s="5">
+        <v>54.4</v>
+      </c>
+      <c r="G122">
+        <v>3</v>
+      </c>
+      <c r="H122">
+        <v>909</v>
+      </c>
+      <c r="L122" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
+        <v>7898662434249</v>
+      </c>
+      <c r="F123" s="5">
+        <v>54.4</v>
+      </c>
+      <c r="G123">
+        <v>3</v>
+      </c>
+      <c r="H123">
+        <v>909</v>
+      </c>
+      <c r="L123" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
         <v>7898662432726</v>
       </c>
-      <c r="F57" s="5">
+      <c r="F124" s="5">
         <v>54.4</v>
       </c>
-      <c r="G57">
-        <v>3</v>
-      </c>
-      <c r="H57">
-        <v>909</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="G124">
+        <v>3</v>
+      </c>
+      <c r="H124">
+        <v>909</v>
+      </c>
+      <c r="L124" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
+        <v>7898662432733</v>
+      </c>
+      <c r="F125" s="5">
+        <v>54.4</v>
+      </c>
+      <c r="G125">
+        <v>3</v>
+      </c>
+      <c r="H125">
+        <v>909</v>
+      </c>
+      <c r="L125" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
+        <v>7898662432665</v>
+      </c>
+      <c r="F126" s="5">
+        <v>54.4</v>
+      </c>
+      <c r="G126">
+        <v>3</v>
+      </c>
+      <c r="H126">
+        <v>909</v>
+      </c>
+      <c r="L126" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
+        <v>7898662432740</v>
+      </c>
+      <c r="F127" s="5">
+        <v>54.4</v>
+      </c>
+      <c r="G127">
+        <v>3</v>
+      </c>
+      <c r="H127">
+        <v>909</v>
+      </c>
+      <c r="L127" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
+        <v>7898662434539</v>
+      </c>
+      <c r="F128" s="5">
+        <v>54.4</v>
+      </c>
+      <c r="G128">
+        <v>3</v>
+      </c>
+      <c r="H128">
+        <v>909</v>
+      </c>
+      <c r="L128" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
+        <v>7898662435109</v>
+      </c>
+      <c r="F129" s="5">
+        <v>54.4</v>
+      </c>
+      <c r="G129">
+        <v>3</v>
+      </c>
+      <c r="H129">
+        <v>909</v>
+      </c>
+      <c r="L129" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A130" s="1">
+        <v>7898662436403</v>
+      </c>
+      <c r="F130" s="5">
+        <v>54.4</v>
+      </c>
+      <c r="G130">
+        <v>3</v>
+      </c>
+      <c r="H130">
+        <v>909</v>
+      </c>
+      <c r="L130" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
+        <v>7898662434546</v>
+      </c>
+      <c r="F131" s="5">
+        <v>54.4</v>
+      </c>
+      <c r="G131">
+        <v>3</v>
+      </c>
+      <c r="H131">
+        <v>909</v>
+      </c>
+      <c r="L131" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
+        <v>7898662432672</v>
+      </c>
+      <c r="F132" s="5">
+        <v>54.4</v>
+      </c>
+      <c r="G132">
+        <v>3</v>
+      </c>
+      <c r="H132">
+        <v>909</v>
+      </c>
+      <c r="L132" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A133" s="1">
+        <v>7898662432719</v>
+      </c>
+      <c r="F133" s="5">
+        <v>54.4</v>
+      </c>
+      <c r="G133">
+        <v>3</v>
+      </c>
+      <c r="H133">
+        <v>909</v>
+      </c>
+      <c r="L133" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A134" s="1">
+        <v>7898662434232</v>
+      </c>
+      <c r="F134" s="5">
+        <v>54.4</v>
+      </c>
+      <c r="G134">
+        <v>3</v>
+      </c>
+      <c r="H134">
+        <v>909</v>
+      </c>
+      <c r="L134" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A135" s="1">
+        <v>7898662432658</v>
+      </c>
+      <c r="F135" s="5">
+        <v>54.4</v>
+      </c>
+      <c r="G135">
+        <v>3</v>
+      </c>
+      <c r="H135">
+        <v>909</v>
+      </c>
+      <c r="L135" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A136" s="1">
+        <v>7898662435116</v>
+      </c>
+      <c r="F136" s="5">
+        <v>54.4</v>
+      </c>
+      <c r="G136">
+        <v>3</v>
+      </c>
+      <c r="H136">
+        <v>909</v>
+      </c>
+      <c r="L136" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A137" s="1">
+        <v>7898662433877</v>
+      </c>
+      <c r="F137" s="5">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="G137">
+        <v>3</v>
+      </c>
+      <c r="H137">
+        <v>909</v>
+      </c>
+      <c r="L137" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A138" s="1">
+        <v>7898662433839</v>
+      </c>
+      <c r="F138" s="5">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="G138">
+        <v>3</v>
+      </c>
+      <c r="H138">
+        <v>909</v>
+      </c>
+      <c r="L138" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A139" s="1">
+        <v>7898662435130</v>
+      </c>
+      <c r="F139" s="5">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="G139">
+        <v>3</v>
+      </c>
+      <c r="H139">
+        <v>909</v>
+      </c>
+      <c r="L139" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A140" s="1">
+        <v>7898662433860</v>
+      </c>
+      <c r="F140" s="5">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="G140">
+        <v>3</v>
+      </c>
+      <c r="H140">
+        <v>909</v>
+      </c>
+      <c r="L140" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A141" s="1">
+        <v>7898662433853</v>
+      </c>
+      <c r="F141" s="5">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="G141">
+        <v>3</v>
+      </c>
+      <c r="H141">
+        <v>909</v>
+      </c>
+      <c r="L141" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A142" s="1">
+        <v>7898662433822</v>
+      </c>
+      <c r="F142" s="5">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="G142">
+        <v>3</v>
+      </c>
+      <c r="H142">
+        <v>909</v>
+      </c>
+      <c r="L142" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A143" s="1">
+        <v>7898662436298</v>
+      </c>
+      <c r="F143" s="5">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="G143">
+        <v>3</v>
+      </c>
+      <c r="H143">
+        <v>909</v>
+      </c>
+      <c r="L143" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A144" s="1">
+        <v>7898662436304</v>
+      </c>
+      <c r="F144" s="5">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="G144">
+        <v>3</v>
+      </c>
+      <c r="H144">
+        <v>909</v>
+      </c>
+      <c r="L144" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A145" s="1">
+        <v>7898662436182</v>
+      </c>
+      <c r="F145" s="5">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="G145">
+        <v>3</v>
+      </c>
+      <c r="H145">
+        <v>909</v>
+      </c>
+      <c r="L145" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A146" s="1">
+        <v>7898662436175</v>
+      </c>
+      <c r="F146" s="5">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="G146">
+        <v>3</v>
+      </c>
+      <c r="H146">
+        <v>909</v>
+      </c>
+      <c r="L146" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A147" s="1">
+        <v>7898662436199</v>
+      </c>
+      <c r="F147" s="5">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="G147">
+        <v>3</v>
+      </c>
+      <c r="H147">
+        <v>909</v>
+      </c>
+      <c r="L147" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A148" s="1">
+        <v>7898662436762</v>
+      </c>
+      <c r="F148" s="5">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="G148">
+        <v>3</v>
+      </c>
+      <c r="H148">
+        <v>909</v>
+      </c>
+      <c r="L148" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A149" s="1">
+        <v>7898662436816</v>
+      </c>
+      <c r="F149" s="5">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="G149">
+        <v>3</v>
+      </c>
+      <c r="H149">
+        <v>909</v>
+      </c>
+      <c r="L149" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A150" s="1">
+        <v>7898662436380</v>
+      </c>
+      <c r="F150" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G150">
+        <v>3</v>
+      </c>
+      <c r="H150">
+        <v>909</v>
+      </c>
+      <c r="L150" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A151" s="1">
+        <v>7898662436397</v>
+      </c>
+      <c r="F151" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G151">
+        <v>3</v>
+      </c>
+      <c r="H151">
+        <v>909</v>
+      </c>
+      <c r="L151" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A152" s="1">
+        <v>7898662436373</v>
+      </c>
+      <c r="F152" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G152">
+        <v>3</v>
+      </c>
+      <c r="H152">
+        <v>909</v>
+      </c>
+      <c r="L152" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A153" s="1">
+        <v>7898662436724</v>
+      </c>
+      <c r="F153" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G153">
+        <v>3</v>
+      </c>
+      <c r="H153">
+        <v>909</v>
+      </c>
+      <c r="L153" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A154" s="1">
+        <v>7898662436731</v>
+      </c>
+      <c r="F154" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G154">
+        <v>3</v>
+      </c>
+      <c r="H154">
+        <v>909</v>
+      </c>
+      <c r="L154" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A155" s="1">
+        <v>7898662436793</v>
+      </c>
+      <c r="F155" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G155">
+        <v>3</v>
+      </c>
+      <c r="H155">
+        <v>909</v>
+      </c>
+      <c r="L155" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A156" s="1">
+        <v>7898662436847</v>
+      </c>
+      <c r="F156" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G156">
+        <v>3</v>
+      </c>
+      <c r="H156">
+        <v>909</v>
+      </c>
+      <c r="L156" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A157" s="1">
+        <v>7898662436106</v>
+      </c>
+      <c r="F157" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G157">
+        <v>3</v>
+      </c>
+      <c r="H157">
+        <v>909</v>
+      </c>
+      <c r="L157" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A158" s="1">
+        <v>7898662435550</v>
+      </c>
+      <c r="F158" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G158">
+        <v>3</v>
+      </c>
+      <c r="H158">
+        <v>909</v>
+      </c>
+      <c r="L158" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A159" s="1">
+        <v>7898662436090</v>
+      </c>
+      <c r="F159" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G159">
+        <v>3</v>
+      </c>
+      <c r="H159">
+        <v>909</v>
+      </c>
+      <c r="L159" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A160" s="1">
+        <v>7898662436427</v>
+      </c>
+      <c r="F160" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G160">
+        <v>6</v>
+      </c>
+      <c r="H160">
+        <v>909</v>
+      </c>
+      <c r="L160" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A161" s="1">
+        <v>7898662436144</v>
+      </c>
+      <c r="F161" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G161">
+        <v>6</v>
+      </c>
+      <c r="H161">
+        <v>909</v>
+      </c>
+      <c r="L161" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A162" s="1">
+        <v>7898662436274</v>
+      </c>
+      <c r="F162" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G162">
+        <v>6</v>
+      </c>
+      <c r="H162">
+        <v>909</v>
+      </c>
+      <c r="L162" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A163" s="1">
+        <v>7898662431057</v>
+      </c>
+      <c r="F163" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G163">
+        <v>6</v>
+      </c>
+      <c r="H163">
+        <v>909</v>
+      </c>
+      <c r="L163" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A164" s="1">
+        <v>7898662430791</v>
+      </c>
+      <c r="F164" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G164">
+        <v>6</v>
+      </c>
+      <c r="H164">
+        <v>909</v>
+      </c>
+      <c r="L164" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A165" s="1">
+        <v>7898662431064</v>
+      </c>
+      <c r="F165" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G165">
+        <v>6</v>
+      </c>
+      <c r="H165">
+        <v>909</v>
+      </c>
+      <c r="L165" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A166" s="1">
+        <v>7898662431002</v>
+      </c>
+      <c r="F166" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G166">
+        <v>6</v>
+      </c>
+      <c r="H166">
+        <v>909</v>
+      </c>
+      <c r="L166" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A167" s="1">
+        <v>7898662430975</v>
+      </c>
+      <c r="F167" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G167">
+        <v>6</v>
+      </c>
+      <c r="H167">
+        <v>909</v>
+      </c>
+      <c r="L167" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A168" s="1">
+        <v>7898662430722</v>
+      </c>
+      <c r="F168" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G168">
+        <v>6</v>
+      </c>
+      <c r="H168">
+        <v>909</v>
+      </c>
+      <c r="L168" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A169" s="1">
+        <v>7898662430487</v>
+      </c>
+      <c r="F169" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G169">
+        <v>6</v>
+      </c>
+      <c r="H169">
+        <v>909</v>
+      </c>
+      <c r="L169" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A170" s="1">
+        <v>7898662430845</v>
+      </c>
+      <c r="F170" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G170">
+        <v>6</v>
+      </c>
+      <c r="H170">
+        <v>909</v>
+      </c>
+      <c r="L170" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A171" s="1">
+        <v>7898662430524</v>
+      </c>
+      <c r="F171" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G171">
+        <v>6</v>
+      </c>
+      <c r="H171">
+        <v>909</v>
+      </c>
+      <c r="L171" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A172" s="1">
+        <v>7898662430531</v>
+      </c>
+      <c r="F172" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G172">
+        <v>6</v>
+      </c>
+      <c r="H172">
+        <v>909</v>
+      </c>
+      <c r="L172" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A173" s="1">
+        <v>7898662430920</v>
+      </c>
+      <c r="F173" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G173">
+        <v>6</v>
+      </c>
+      <c r="H173">
+        <v>909</v>
+      </c>
+      <c r="L173" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A174" s="1">
+        <v>7898662430883</v>
+      </c>
+      <c r="F174" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G174">
+        <v>6</v>
+      </c>
+      <c r="H174">
+        <v>909</v>
+      </c>
+      <c r="L174" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A175" s="1">
+        <v>7898662430470</v>
+      </c>
+      <c r="F175" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G175">
+        <v>6</v>
+      </c>
+      <c r="H175">
+        <v>909</v>
+      </c>
+      <c r="L175" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A176" s="1">
+        <v>7898662430517</v>
+      </c>
+      <c r="F176" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G176">
+        <v>6</v>
+      </c>
+      <c r="H176">
+        <v>909</v>
+      </c>
+      <c r="L176" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A177" s="1">
+        <v>7898662430401</v>
+      </c>
+      <c r="F177" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G177">
+        <v>6</v>
+      </c>
+      <c r="H177">
+        <v>909</v>
+      </c>
+      <c r="L177" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A178" s="1">
+        <v>7898662433297</v>
+      </c>
+      <c r="F178" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G178">
+        <v>6</v>
+      </c>
+      <c r="H178">
+        <v>909</v>
+      </c>
+      <c r="L178" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A179" s="1">
+        <v>7898662434430</v>
+      </c>
+      <c r="F179" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G179">
+        <v>6</v>
+      </c>
+      <c r="H179">
+        <v>909</v>
+      </c>
+      <c r="L179" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A180" s="1">
+        <v>7898662435093</v>
+      </c>
+      <c r="F180" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G180">
+        <v>6</v>
+      </c>
+      <c r="H180">
+        <v>909</v>
+      </c>
+      <c r="L180" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A181" s="1">
+        <v>7898662430425</v>
+      </c>
+      <c r="F181" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G181">
+        <v>6</v>
+      </c>
+      <c r="H181">
+        <v>909</v>
+      </c>
+      <c r="L181" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A182" s="1">
+        <v>7898662436434</v>
+      </c>
+      <c r="F182" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G182">
+        <v>6</v>
+      </c>
+      <c r="H182">
+        <v>909</v>
+      </c>
+      <c r="L182" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A183" s="1">
+        <v>7898662436137</v>
+      </c>
+      <c r="F183" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G183">
+        <v>6</v>
+      </c>
+      <c r="H183">
+        <v>909</v>
+      </c>
+      <c r="L183" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A184" s="1">
+        <v>7898662436267</v>
+      </c>
+      <c r="F184" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G184">
+        <v>6</v>
+      </c>
+      <c r="H184">
+        <v>909</v>
+      </c>
+      <c r="L184" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A185" s="1">
+        <v>7898662430951</v>
+      </c>
+      <c r="F185" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G185">
+        <v>6</v>
+      </c>
+      <c r="H185">
+        <v>909</v>
+      </c>
+      <c r="L185" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A186" s="1">
+        <v>7898662430869</v>
+      </c>
+      <c r="F186" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G186">
+        <v>6</v>
+      </c>
+      <c r="H186">
+        <v>909</v>
+      </c>
+      <c r="L186" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A187" s="1">
+        <v>7898662430913</v>
+      </c>
+      <c r="F187" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G187">
+        <v>6</v>
+      </c>
+      <c r="H187">
+        <v>909</v>
+      </c>
+      <c r="L187" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A188" s="1">
+        <v>7898662430852</v>
+      </c>
+      <c r="F188" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G188">
+        <v>6</v>
+      </c>
+      <c r="H188">
+        <v>909</v>
+      </c>
+      <c r="L188" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A189" s="1">
+        <v>7898662430463</v>
+      </c>
+      <c r="F189" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G189">
+        <v>6</v>
+      </c>
+      <c r="H189">
+        <v>909</v>
+      </c>
+      <c r="L189" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A190" s="1">
+        <v>7898662430746</v>
+      </c>
+      <c r="F190" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G190">
+        <v>6</v>
+      </c>
+      <c r="H190">
+        <v>909</v>
+      </c>
+      <c r="L190" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A191" s="1">
+        <v>7898662430418</v>
+      </c>
+      <c r="F191" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G191">
+        <v>6</v>
+      </c>
+      <c r="H191">
+        <v>909</v>
+      </c>
+      <c r="L191" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A192" s="1">
+        <v>7898662430500</v>
+      </c>
+      <c r="F192" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G192">
+        <v>6</v>
+      </c>
+      <c r="H192">
+        <v>909</v>
+      </c>
+      <c r="L192" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A193" s="1">
+        <v>7898662434201</v>
+      </c>
+      <c r="F193" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G193">
+        <v>6</v>
+      </c>
+      <c r="H193">
+        <v>909</v>
+      </c>
+      <c r="L193" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A194" s="1">
+        <v>7898662434423</v>
+      </c>
+      <c r="F194" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G194">
+        <v>6</v>
+      </c>
+      <c r="H194">
+        <v>909</v>
+      </c>
+      <c r="L194" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A195" s="1">
+        <v>7898662434966</v>
+      </c>
+      <c r="F195" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G195">
+        <v>6</v>
+      </c>
+      <c r="H195">
+        <v>909</v>
+      </c>
+      <c r="L195" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A196" s="1">
+        <v>7898662430555</v>
+      </c>
+      <c r="F196" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G196">
+        <v>6</v>
+      </c>
+      <c r="H196">
+        <v>909</v>
+      </c>
+      <c r="L196" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A197" s="1">
+        <v>7898662435147</v>
+      </c>
+      <c r="F197" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G197">
+        <v>6</v>
+      </c>
+      <c r="H197">
+        <v>909</v>
+      </c>
+      <c r="L197" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A198" s="1">
+        <v>7898662435208</v>
+      </c>
+      <c r="F198" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G198">
+        <v>6</v>
+      </c>
+      <c r="H198">
+        <v>909</v>
+      </c>
+      <c r="L198" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A199" s="1">
+        <v>7898662435123</v>
+      </c>
+      <c r="F199" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G199">
+        <v>6</v>
+      </c>
+      <c r="H199">
+        <v>909</v>
+      </c>
+      <c r="L199" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A200" s="1">
+        <v>7898662435031</v>
+      </c>
+      <c r="F200" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G200">
+        <v>6</v>
+      </c>
+      <c r="H200">
+        <v>909</v>
+      </c>
+      <c r="L200" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A201" s="1">
+        <v>7898662436410</v>
+      </c>
+      <c r="F201" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G201">
+        <v>6</v>
+      </c>
+      <c r="H201">
+        <v>909</v>
+      </c>
+      <c r="L201" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A202" s="1">
+        <v>7898662434249</v>
+      </c>
+      <c r="F202" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G202">
+        <v>6</v>
+      </c>
+      <c r="H202">
+        <v>909</v>
+      </c>
+      <c r="L202" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A203" s="1">
+        <v>7898662432726</v>
+      </c>
+      <c r="F203" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G203">
+        <v>6</v>
+      </c>
+      <c r="H203">
+        <v>909</v>
+      </c>
+      <c r="L203" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A204" s="1">
+        <v>7898662432733</v>
+      </c>
+      <c r="F204" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G204">
+        <v>6</v>
+      </c>
+      <c r="H204">
+        <v>909</v>
+      </c>
+      <c r="L204" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A205" s="1">
+        <v>7898662432665</v>
+      </c>
+      <c r="F205" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G205">
+        <v>6</v>
+      </c>
+      <c r="H205">
+        <v>909</v>
+      </c>
+      <c r="L205" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A206" s="1">
+        <v>7898662432740</v>
+      </c>
+      <c r="F206" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G206">
+        <v>6</v>
+      </c>
+      <c r="H206">
+        <v>909</v>
+      </c>
+      <c r="L206" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A207" s="1">
+        <v>7898662434539</v>
+      </c>
+      <c r="F207" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G207">
+        <v>6</v>
+      </c>
+      <c r="H207">
+        <v>909</v>
+      </c>
+      <c r="L207" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A208" s="1">
+        <v>7898662435109</v>
+      </c>
+      <c r="F208" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G208">
+        <v>6</v>
+      </c>
+      <c r="H208">
+        <v>909</v>
+      </c>
+      <c r="L208" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A209" s="1">
+        <v>7898662436403</v>
+      </c>
+      <c r="F209" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G209">
+        <v>6</v>
+      </c>
+      <c r="H209">
+        <v>909</v>
+      </c>
+      <c r="L209" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A210" s="1">
+        <v>7898662434546</v>
+      </c>
+      <c r="F210" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G210">
+        <v>6</v>
+      </c>
+      <c r="H210">
+        <v>909</v>
+      </c>
+      <c r="L210" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A211" s="1">
+        <v>7898662432672</v>
+      </c>
+      <c r="F211" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G211">
+        <v>6</v>
+      </c>
+      <c r="H211">
+        <v>909</v>
+      </c>
+      <c r="L211" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A212" s="1">
+        <v>7898662432719</v>
+      </c>
+      <c r="F212" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G212">
+        <v>6</v>
+      </c>
+      <c r="H212">
+        <v>909</v>
+      </c>
+      <c r="L212" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A213" s="1">
+        <v>7898662434232</v>
+      </c>
+      <c r="F213" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G213">
+        <v>6</v>
+      </c>
+      <c r="H213">
+        <v>909</v>
+      </c>
+      <c r="L213" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A214" s="1">
+        <v>7898662432658</v>
+      </c>
+      <c r="F214" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G214">
+        <v>6</v>
+      </c>
+      <c r="H214">
+        <v>909</v>
+      </c>
+      <c r="L214" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A215" s="1">
+        <v>7898662435116</v>
+      </c>
+      <c r="F215" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G215">
+        <v>6</v>
+      </c>
+      <c r="H215">
+        <v>909</v>
+      </c>
+      <c r="L215" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A216" s="1">
+        <v>7898662433877</v>
+      </c>
+      <c r="F216" s="5">
+        <v>11.66</v>
+      </c>
+      <c r="G216">
+        <v>6</v>
+      </c>
+      <c r="H216">
+        <v>909</v>
+      </c>
+      <c r="L216" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A217" s="1">
+        <v>7898662433839</v>
+      </c>
+      <c r="F217" s="5">
+        <v>11.66</v>
+      </c>
+      <c r="G217">
+        <v>6</v>
+      </c>
+      <c r="H217">
+        <v>909</v>
+      </c>
+      <c r="L217" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A218" s="1">
+        <v>7898662435130</v>
+      </c>
+      <c r="F218" s="5">
+        <v>11.66</v>
+      </c>
+      <c r="G218">
+        <v>6</v>
+      </c>
+      <c r="H218">
+        <v>909</v>
+      </c>
+      <c r="L218" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A219" s="1">
+        <v>7898662433860</v>
+      </c>
+      <c r="F219" s="5">
+        <v>11.66</v>
+      </c>
+      <c r="G219">
+        <v>6</v>
+      </c>
+      <c r="H219">
+        <v>909</v>
+      </c>
+      <c r="L219" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A220" s="1">
+        <v>7898662433853</v>
+      </c>
+      <c r="F220" s="5">
+        <v>11.66</v>
+      </c>
+      <c r="G220">
+        <v>6</v>
+      </c>
+      <c r="H220">
+        <v>909</v>
+      </c>
+      <c r="L220" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A221" s="1">
+        <v>7898662433822</v>
+      </c>
+      <c r="F221" s="5">
+        <v>11.66</v>
+      </c>
+      <c r="G221">
+        <v>6</v>
+      </c>
+      <c r="H221">
+        <v>909</v>
+      </c>
+      <c r="L221" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A222" s="1">
+        <v>7898662436298</v>
+      </c>
+      <c r="F222" s="5">
+        <v>17.95</v>
+      </c>
+      <c r="G222">
+        <v>6</v>
+      </c>
+      <c r="H222">
+        <v>909</v>
+      </c>
+      <c r="L222" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A223" s="1">
+        <v>7898662436304</v>
+      </c>
+      <c r="F223" s="5">
+        <v>17.95</v>
+      </c>
+      <c r="G223">
+        <v>6</v>
+      </c>
+      <c r="H223">
+        <v>909</v>
+      </c>
+      <c r="L223" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A224" s="1">
+        <v>7898662436182</v>
+      </c>
+      <c r="F224" s="5">
+        <v>17.95</v>
+      </c>
+      <c r="G224">
+        <v>6</v>
+      </c>
+      <c r="H224">
+        <v>909</v>
+      </c>
+      <c r="L224" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A225" s="1">
+        <v>7898662436175</v>
+      </c>
+      <c r="F225" s="5">
+        <v>17.95</v>
+      </c>
+      <c r="G225">
+        <v>6</v>
+      </c>
+      <c r="H225">
+        <v>909</v>
+      </c>
+      <c r="L225" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A226" s="1">
+        <v>7898662436199</v>
+      </c>
+      <c r="F226" s="5">
+        <v>17.95</v>
+      </c>
+      <c r="G226">
+        <v>6</v>
+      </c>
+      <c r="H226">
+        <v>909</v>
+      </c>
+      <c r="L226" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A227" s="1">
+        <v>7898662436762</v>
+      </c>
+      <c r="F227" s="5">
+        <v>17.95</v>
+      </c>
+      <c r="G227">
+        <v>6</v>
+      </c>
+      <c r="H227">
+        <v>909</v>
+      </c>
+      <c r="L227" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A228" s="1">
+        <v>7898662436816</v>
+      </c>
+      <c r="F228" s="5">
+        <v>17.95</v>
+      </c>
+      <c r="G228">
+        <v>6</v>
+      </c>
+      <c r="H228">
+        <v>909</v>
+      </c>
+      <c r="L228" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A229" s="1">
+        <v>7898662436380</v>
+      </c>
+      <c r="F229" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G229">
+        <v>6</v>
+      </c>
+      <c r="H229">
+        <v>909</v>
+      </c>
+      <c r="L229" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A230" s="1">
+        <v>7898662436397</v>
+      </c>
+      <c r="F230" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G230">
+        <v>6</v>
+      </c>
+      <c r="H230">
+        <v>909</v>
+      </c>
+      <c r="L230" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A231" s="1">
+        <v>7898662436373</v>
+      </c>
+      <c r="F231" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G231">
+        <v>6</v>
+      </c>
+      <c r="H231">
+        <v>909</v>
+      </c>
+      <c r="L231" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A232" s="1">
+        <v>7898662436724</v>
+      </c>
+      <c r="F232" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G232">
+        <v>6</v>
+      </c>
+      <c r="H232">
+        <v>909</v>
+      </c>
+      <c r="L232" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A233" s="1">
+        <v>7898662436731</v>
+      </c>
+      <c r="F233" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G233">
+        <v>6</v>
+      </c>
+      <c r="H233">
+        <v>909</v>
+      </c>
+      <c r="L233" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A234" s="1">
+        <v>7898662436793</v>
+      </c>
+      <c r="F234" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G234">
+        <v>6</v>
+      </c>
+      <c r="H234">
+        <v>909</v>
+      </c>
+      <c r="L234" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A235" s="1">
+        <v>7898662436847</v>
+      </c>
+      <c r="F235" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G235">
+        <v>6</v>
+      </c>
+      <c r="H235">
+        <v>909</v>
+      </c>
+      <c r="L235" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A236" s="1">
+        <v>7898662436106</v>
+      </c>
+      <c r="F236" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G236">
+        <v>6</v>
+      </c>
+      <c r="H236">
+        <v>909</v>
+      </c>
+      <c r="L236" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A237" s="1">
+        <v>7898662435550</v>
+      </c>
+      <c r="F237" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G237">
+        <v>6</v>
+      </c>
+      <c r="H237">
+        <v>909</v>
+      </c>
+      <c r="L237" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A238" s="1">
+        <v>7898662436090</v>
+      </c>
+      <c r="F238" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G238">
+        <v>6</v>
+      </c>
+      <c r="H238">
+        <v>909</v>
+      </c>
+      <c r="L238" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A239" s="1">
+        <v>7898662436427</v>
+      </c>
+      <c r="F239" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G239">
+        <v>5</v>
+      </c>
+      <c r="H239">
+        <v>909</v>
+      </c>
+      <c r="L239" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A240" s="1">
+        <v>7898662436144</v>
+      </c>
+      <c r="F240" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G240">
+        <v>5</v>
+      </c>
+      <c r="H240">
+        <v>909</v>
+      </c>
+      <c r="L240" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A241" s="1">
+        <v>7898662436274</v>
+      </c>
+      <c r="F241" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G241">
+        <v>5</v>
+      </c>
+      <c r="H241">
+        <v>909</v>
+      </c>
+      <c r="L241" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A242" s="1">
+        <v>7898662431057</v>
+      </c>
+      <c r="F242" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G242">
+        <v>5</v>
+      </c>
+      <c r="H242">
+        <v>909</v>
+      </c>
+      <c r="L242" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A243" s="1">
+        <v>7898662430791</v>
+      </c>
+      <c r="F243" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G243">
+        <v>5</v>
+      </c>
+      <c r="H243">
+        <v>909</v>
+      </c>
+      <c r="L243" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A244" s="1">
+        <v>7898662431064</v>
+      </c>
+      <c r="F244" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G244">
+        <v>5</v>
+      </c>
+      <c r="H244">
+        <v>909</v>
+      </c>
+      <c r="L244" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A245" s="1">
+        <v>7898662431002</v>
+      </c>
+      <c r="F245" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G245">
+        <v>5</v>
+      </c>
+      <c r="H245">
+        <v>909</v>
+      </c>
+      <c r="L245" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A246" s="1">
+        <v>7898662430975</v>
+      </c>
+      <c r="F246" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G246">
+        <v>5</v>
+      </c>
+      <c r="H246">
+        <v>909</v>
+      </c>
+      <c r="L246" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A247" s="1">
+        <v>7898662430722</v>
+      </c>
+      <c r="F247" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G247">
+        <v>5</v>
+      </c>
+      <c r="H247">
+        <v>909</v>
+      </c>
+      <c r="L247" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A248" s="1">
+        <v>7898662430487</v>
+      </c>
+      <c r="F248" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G248">
+        <v>5</v>
+      </c>
+      <c r="H248">
+        <v>909</v>
+      </c>
+      <c r="L248" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A249" s="1">
+        <v>7898662430845</v>
+      </c>
+      <c r="F249" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G249">
+        <v>5</v>
+      </c>
+      <c r="H249">
+        <v>909</v>
+      </c>
+      <c r="L249" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A250" s="1">
+        <v>7898662430524</v>
+      </c>
+      <c r="F250" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G250">
+        <v>5</v>
+      </c>
+      <c r="H250">
+        <v>909</v>
+      </c>
+      <c r="L250" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A251" s="1">
+        <v>7898662430531</v>
+      </c>
+      <c r="F251" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G251">
+        <v>5</v>
+      </c>
+      <c r="H251">
+        <v>909</v>
+      </c>
+      <c r="L251" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A252" s="1">
+        <v>7898662430920</v>
+      </c>
+      <c r="F252" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G252">
+        <v>5</v>
+      </c>
+      <c r="H252">
+        <v>909</v>
+      </c>
+      <c r="L252" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A253" s="1">
+        <v>7898662430883</v>
+      </c>
+      <c r="F253" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G253">
+        <v>5</v>
+      </c>
+      <c r="H253">
+        <v>909</v>
+      </c>
+      <c r="L253" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A254" s="1">
+        <v>7898662430470</v>
+      </c>
+      <c r="F254" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G254">
+        <v>5</v>
+      </c>
+      <c r="H254">
+        <v>909</v>
+      </c>
+      <c r="L254" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A255" s="1">
+        <v>7898662430517</v>
+      </c>
+      <c r="F255" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G255">
+        <v>5</v>
+      </c>
+      <c r="H255">
+        <v>909</v>
+      </c>
+      <c r="L255" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A256" s="1">
+        <v>7898662430401</v>
+      </c>
+      <c r="F256" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G256">
+        <v>5</v>
+      </c>
+      <c r="H256">
+        <v>909</v>
+      </c>
+      <c r="L256" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A257" s="1">
+        <v>7898662430807</v>
+      </c>
+      <c r="F257" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G257">
+        <v>5</v>
+      </c>
+      <c r="H257">
+        <v>909</v>
+      </c>
+      <c r="L257" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A258" s="1">
+        <v>7898662434430</v>
+      </c>
+      <c r="F258" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G258">
+        <v>5</v>
+      </c>
+      <c r="H258">
+        <v>909</v>
+      </c>
+      <c r="L258" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A259" s="1">
+        <v>7898662435093</v>
+      </c>
+      <c r="F259" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G259">
+        <v>5</v>
+      </c>
+      <c r="H259">
+        <v>909</v>
+      </c>
+      <c r="L259" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A260" s="1">
+        <v>7898662430425</v>
+      </c>
+      <c r="F260" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G260">
+        <v>5</v>
+      </c>
+      <c r="H260">
+        <v>909</v>
+      </c>
+      <c r="L260" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A261" s="1">
+        <v>7898662436434</v>
+      </c>
+      <c r="F261" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G261">
+        <v>5</v>
+      </c>
+      <c r="H261">
+        <v>909</v>
+      </c>
+      <c r="L261" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A262" s="1">
+        <v>7898662436137</v>
+      </c>
+      <c r="F262" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G262">
+        <v>5</v>
+      </c>
+      <c r="H262">
+        <v>909</v>
+      </c>
+      <c r="L262" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A263" s="1">
+        <v>7898662436267</v>
+      </c>
+      <c r="F263" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G263">
+        <v>5</v>
+      </c>
+      <c r="H263">
+        <v>909</v>
+      </c>
+      <c r="L263" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A264" s="1">
+        <v>7898662430951</v>
+      </c>
+      <c r="F264" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G264">
+        <v>5</v>
+      </c>
+      <c r="H264">
+        <v>909</v>
+      </c>
+      <c r="L264" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A265" s="1">
+        <v>7898662430869</v>
+      </c>
+      <c r="F265" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G265">
+        <v>5</v>
+      </c>
+      <c r="H265">
+        <v>909</v>
+      </c>
+      <c r="L265" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A266" s="1">
+        <v>7898662430913</v>
+      </c>
+      <c r="F266" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G266">
+        <v>5</v>
+      </c>
+      <c r="H266">
+        <v>909</v>
+      </c>
+      <c r="L266" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A267" s="1">
+        <v>7898662430852</v>
+      </c>
+      <c r="F267" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G267">
+        <v>5</v>
+      </c>
+      <c r="H267">
+        <v>909</v>
+      </c>
+      <c r="L267" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A268" s="1">
+        <v>7898662430463</v>
+      </c>
+      <c r="F268" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G268">
+        <v>5</v>
+      </c>
+      <c r="H268">
+        <v>909</v>
+      </c>
+      <c r="L268" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A269" s="1">
+        <v>7898662430746</v>
+      </c>
+      <c r="F269" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G269">
+        <v>5</v>
+      </c>
+      <c r="H269">
+        <v>909</v>
+      </c>
+      <c r="L269" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A270" s="1">
+        <v>7898662430418</v>
+      </c>
+      <c r="F270" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G270">
+        <v>5</v>
+      </c>
+      <c r="H270">
+        <v>909</v>
+      </c>
+      <c r="L270" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A271" s="1">
+        <v>7898662430500</v>
+      </c>
+      <c r="F271" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G271">
+        <v>5</v>
+      </c>
+      <c r="H271">
+        <v>909</v>
+      </c>
+      <c r="L271" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A272" s="1">
+        <v>7898662434201</v>
+      </c>
+      <c r="F272" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G272">
+        <v>5</v>
+      </c>
+      <c r="H272">
+        <v>909</v>
+      </c>
+      <c r="L272" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A273" s="1">
+        <v>7898662434423</v>
+      </c>
+      <c r="F273" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G273">
+        <v>5</v>
+      </c>
+      <c r="H273">
+        <v>909</v>
+      </c>
+      <c r="L273" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A274" s="1">
+        <v>7898662434966</v>
+      </c>
+      <c r="F274" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G274">
+        <v>5</v>
+      </c>
+      <c r="H274">
+        <v>909</v>
+      </c>
+      <c r="L274" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A275" s="1">
+        <v>7898662430555</v>
+      </c>
+      <c r="F275" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G275">
+        <v>5</v>
+      </c>
+      <c r="H275">
+        <v>909</v>
+      </c>
+      <c r="L275" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A276" s="1">
+        <v>7898662435147</v>
+      </c>
+      <c r="F276" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G276">
+        <v>5</v>
+      </c>
+      <c r="H276">
+        <v>909</v>
+      </c>
+      <c r="L276" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A277" s="1">
+        <v>7898662435208</v>
+      </c>
+      <c r="F277" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G277">
+        <v>5</v>
+      </c>
+      <c r="H277">
+        <v>909</v>
+      </c>
+      <c r="L277" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A278" s="1">
+        <v>7898662435123</v>
+      </c>
+      <c r="F278" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G278">
+        <v>5</v>
+      </c>
+      <c r="H278">
+        <v>909</v>
+      </c>
+      <c r="L278" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A279" s="1">
+        <v>7898662435031</v>
+      </c>
+      <c r="F279" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="G279">
+        <v>5</v>
+      </c>
+      <c r="H279">
+        <v>909</v>
+      </c>
+      <c r="L279" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A280" s="1">
+        <v>7898662436410</v>
+      </c>
+      <c r="F280" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G280">
+        <v>5</v>
+      </c>
+      <c r="H280">
+        <v>909</v>
+      </c>
+      <c r="L280" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A281" s="1">
+        <v>7898662434249</v>
+      </c>
+      <c r="F281" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G281">
+        <v>5</v>
+      </c>
+      <c r="H281">
+        <v>909</v>
+      </c>
+      <c r="L281" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A282" s="1">
+        <v>7898662432726</v>
+      </c>
+      <c r="F282" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G282">
+        <v>5</v>
+      </c>
+      <c r="H282">
+        <v>909</v>
+      </c>
+      <c r="L282" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A283" s="1">
+        <v>7898662432733</v>
+      </c>
+      <c r="F283" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G283">
+        <v>5</v>
+      </c>
+      <c r="H283">
+        <v>909</v>
+      </c>
+      <c r="L283" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A284" s="1">
+        <v>7898662432665</v>
+      </c>
+      <c r="F284" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G284">
+        <v>5</v>
+      </c>
+      <c r="H284">
+        <v>909</v>
+      </c>
+      <c r="L284" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A285" s="1">
+        <v>7898662432740</v>
+      </c>
+      <c r="F285" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G285">
+        <v>5</v>
+      </c>
+      <c r="H285">
+        <v>909</v>
+      </c>
+      <c r="L285" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A286" s="1">
+        <v>7898662434539</v>
+      </c>
+      <c r="F286" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G286">
+        <v>5</v>
+      </c>
+      <c r="H286">
+        <v>909</v>
+      </c>
+      <c r="L286" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A287" s="1">
+        <v>7898662435109</v>
+      </c>
+      <c r="F287" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G287">
+        <v>5</v>
+      </c>
+      <c r="H287">
+        <v>909</v>
+      </c>
+      <c r="L287" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A288" s="1">
+        <v>7898662436403</v>
+      </c>
+      <c r="F288" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G288">
+        <v>5</v>
+      </c>
+      <c r="H288">
+        <v>909</v>
+      </c>
+      <c r="L288" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="289" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A289" s="1">
+        <v>7898662434546</v>
+      </c>
+      <c r="F289" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G289">
+        <v>5</v>
+      </c>
+      <c r="H289">
+        <v>909</v>
+      </c>
+      <c r="L289" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A290" s="1">
+        <v>7898662432672</v>
+      </c>
+      <c r="F290" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G290">
+        <v>5</v>
+      </c>
+      <c r="H290">
+        <v>909</v>
+      </c>
+      <c r="L290" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A291" s="1">
+        <v>7898662432719</v>
+      </c>
+      <c r="F291" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G291">
+        <v>5</v>
+      </c>
+      <c r="H291">
+        <v>909</v>
+      </c>
+      <c r="L291" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="292" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A292" s="1">
+        <v>7898662434232</v>
+      </c>
+      <c r="F292" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G292">
+        <v>5</v>
+      </c>
+      <c r="H292">
+        <v>909</v>
+      </c>
+      <c r="L292" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="293" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A293" s="1">
+        <v>7898662432658</v>
+      </c>
+      <c r="F293" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G293">
+        <v>5</v>
+      </c>
+      <c r="H293">
+        <v>909</v>
+      </c>
+      <c r="L293" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A294" s="1">
+        <v>7898662435116</v>
+      </c>
+      <c r="F294" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="G294">
+        <v>5</v>
+      </c>
+      <c r="H294">
+        <v>909</v>
+      </c>
+      <c r="L294" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A295" s="1">
+        <v>7898662433877</v>
+      </c>
+      <c r="F295" s="5">
+        <v>11.66</v>
+      </c>
+      <c r="G295">
+        <v>5</v>
+      </c>
+      <c r="H295">
+        <v>909</v>
+      </c>
+      <c r="L295" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A296" s="1">
+        <v>7898662433839</v>
+      </c>
+      <c r="F296" s="5">
+        <v>11.66</v>
+      </c>
+      <c r="G296">
+        <v>5</v>
+      </c>
+      <c r="H296">
+        <v>909</v>
+      </c>
+      <c r="L296" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="297" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A297" s="1">
+        <v>7898662435130</v>
+      </c>
+      <c r="F297" s="5">
+        <v>11.66</v>
+      </c>
+      <c r="G297">
+        <v>5</v>
+      </c>
+      <c r="H297">
+        <v>909</v>
+      </c>
+      <c r="L297" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="298" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A298" s="1">
+        <v>7898662433860</v>
+      </c>
+      <c r="F298" s="5">
+        <v>11.66</v>
+      </c>
+      <c r="G298">
+        <v>5</v>
+      </c>
+      <c r="H298">
+        <v>909</v>
+      </c>
+      <c r="L298" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="299" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A299" s="1">
+        <v>7898662433853</v>
+      </c>
+      <c r="F299" s="5">
+        <v>11.66</v>
+      </c>
+      <c r="G299">
+        <v>5</v>
+      </c>
+      <c r="H299">
+        <v>909</v>
+      </c>
+      <c r="L299" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="300" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A300" s="1">
+        <v>7898662433822</v>
+      </c>
+      <c r="F300" s="5">
+        <v>11.66</v>
+      </c>
+      <c r="G300">
+        <v>5</v>
+      </c>
+      <c r="H300">
+        <v>909</v>
+      </c>
+      <c r="L300" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A301" s="1">
+        <v>7898662436298</v>
+      </c>
+      <c r="F301" s="5">
+        <v>17.95</v>
+      </c>
+      <c r="G301">
+        <v>5</v>
+      </c>
+      <c r="H301">
+        <v>909</v>
+      </c>
+      <c r="L301" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="302" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A302" s="1">
+        <v>7898662436304</v>
+      </c>
+      <c r="F302" s="5">
+        <v>17.95</v>
+      </c>
+      <c r="G302">
+        <v>5</v>
+      </c>
+      <c r="H302">
+        <v>909</v>
+      </c>
+      <c r="L302" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="303" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A303" s="1">
+        <v>7898662436182</v>
+      </c>
+      <c r="F303" s="5">
+        <v>17.95</v>
+      </c>
+      <c r="G303">
+        <v>5</v>
+      </c>
+      <c r="H303">
+        <v>909</v>
+      </c>
+      <c r="L303" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="304" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A304" s="1">
+        <v>7898662436175</v>
+      </c>
+      <c r="F304" s="5">
+        <v>17.95</v>
+      </c>
+      <c r="G304">
+        <v>5</v>
+      </c>
+      <c r="H304">
+        <v>909</v>
+      </c>
+      <c r="L304" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A305" s="1">
+        <v>7898662436199</v>
+      </c>
+      <c r="F305" s="5">
+        <v>17.95</v>
+      </c>
+      <c r="G305">
+        <v>5</v>
+      </c>
+      <c r="H305">
+        <v>909</v>
+      </c>
+      <c r="L305" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A306" s="1">
+        <v>7898662436762</v>
+      </c>
+      <c r="F306" s="5">
+        <v>17.95</v>
+      </c>
+      <c r="G306">
+        <v>5</v>
+      </c>
+      <c r="H306">
+        <v>909</v>
+      </c>
+      <c r="L306" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A307" s="1">
+        <v>7898662436816</v>
+      </c>
+      <c r="F307" s="5">
+        <v>17.95</v>
+      </c>
+      <c r="G307">
+        <v>5</v>
+      </c>
+      <c r="H307">
+        <v>909</v>
+      </c>
+      <c r="L307" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A308" s="1">
+        <v>7898662436380</v>
+      </c>
+      <c r="F308" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G308">
+        <v>5</v>
+      </c>
+      <c r="H308">
+        <v>909</v>
+      </c>
+      <c r="L308" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A309" s="1">
+        <v>7898662436397</v>
+      </c>
+      <c r="F309" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G309">
+        <v>5</v>
+      </c>
+      <c r="H309">
+        <v>909</v>
+      </c>
+      <c r="L309" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A310" s="1">
+        <v>7898662436373</v>
+      </c>
+      <c r="F310" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G310">
+        <v>5</v>
+      </c>
+      <c r="H310">
+        <v>909</v>
+      </c>
+      <c r="L310" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A311" s="1">
+        <v>7898662436724</v>
+      </c>
+      <c r="F311" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G311">
+        <v>5</v>
+      </c>
+      <c r="H311">
+        <v>909</v>
+      </c>
+      <c r="L311" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A312" s="1">
+        <v>7898662436731</v>
+      </c>
+      <c r="F312" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G312">
+        <v>5</v>
+      </c>
+      <c r="H312">
+        <v>909</v>
+      </c>
+      <c r="L312" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A313" s="1">
+        <v>7898662436793</v>
+      </c>
+      <c r="F313" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G313">
+        <v>5</v>
+      </c>
+      <c r="H313">
+        <v>909</v>
+      </c>
+      <c r="L313" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A314" s="1">
+        <v>7898662436847</v>
+      </c>
+      <c r="F314" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G314">
+        <v>5</v>
+      </c>
+      <c r="H314">
+        <v>909</v>
+      </c>
+      <c r="L314" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A315" s="1">
+        <v>7898662436106</v>
+      </c>
+      <c r="F315" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G315">
+        <v>5</v>
+      </c>
+      <c r="H315">
+        <v>909</v>
+      </c>
+      <c r="L315" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A316" s="1">
+        <v>7898662435550</v>
+      </c>
+      <c r="F316" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G316">
+        <v>5</v>
+      </c>
+      <c r="H316">
+        <v>909</v>
+      </c>
+      <c r="L316" s="3">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A317" s="1">
+        <v>7898662436090</v>
+      </c>
+      <c r="F317" s="5">
+        <v>25.3</v>
+      </c>
+      <c r="G317">
+        <v>5</v>
+      </c>
+      <c r="H317">
+        <v>909</v>
+      </c>
+      <c r="L317" s="3">
         <v>46387</v>
       </c>
     </row>
